--- a/output/roomself_excel/14413.xlsx
+++ b/output/roomself_excel/14413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312324</v>
+        <v>72063</v>
       </c>
       <c r="D2" t="n">
-        <v>5404</v>
+        <v>2587</v>
       </c>
       <c r="E2" t="n">
-        <v>777</v>
+        <v>639</v>
       </c>
       <c r="F2" t="n">
-        <v>648</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3">
@@ -502,6 +502,28 @@
       </c>
       <c r="F3" t="n">
         <v>164</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>240261</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4040</v>
+      </c>
+      <c r="E4" t="n">
+        <v>646</v>
+      </c>
+      <c r="F4" t="n">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14413.xlsx
+++ b/output/roomself_excel/14413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,11 +540,60 @@
       <c r="D2" t="n">
         <v>2587</v>
       </c>
-      <c r="E2" t="n">
-        <v>639</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>161</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>104</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>131</v>
+      </c>
+      <c r="M2" t="n">
+        <v>27</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>96</v>
+      </c>
+      <c r="P2" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>52</v>
+      </c>
+      <c r="S2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +611,53 @@
       <c r="D3" t="n">
         <v>1411</v>
       </c>
-      <c r="E3" t="n">
-        <v>390</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>164</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>133</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>65</v>
+      </c>
+      <c r="P3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +674,60 @@
       <c r="D4" t="n">
         <v>4040</v>
       </c>
-      <c r="E4" t="n">
-        <v>646</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>622</v>
+        <v>191</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>220</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>570</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>397</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
